--- a/data/trans_camb/IP07_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>15,65</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,13</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 15,59</t>
+          <t>-1,29; 15,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 23,21</t>
+          <t>3,98; 20,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 13,95</t>
+          <t>-20,81; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 15,49</t>
+          <t>-2,34; 15,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 20,16</t>
+          <t>7,41; 22,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 6,61</t>
+          <t>-3,97; 13,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 12,39</t>
+          <t>1,52; 12,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 19,52</t>
+          <t>7,86; 19,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 7,18</t>
+          <t>-10,01; 6,82</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-7,42%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>21,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,81%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,3%</t>
+          <t>-0,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 23,26</t>
+          <t>-1,55; 24,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 34,92</t>
+          <t>5,31; 30,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 21,64</t>
+          <t>-27,97; 8,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 22,9</t>
+          <t>-3,09; 23,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 30,31</t>
+          <t>10,01; 35,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 9,51</t>
+          <t>-5,21; 20,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 18,17</t>
+          <t>2,02; 18,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,94; 29,22</t>
+          <t>10,67; 28,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 10,55</t>
+          <t>-13,39; 9,88</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,47</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,79</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,19</t>
+          <t>-8,75; 5,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 19,25</t>
+          <t>6,66; 18,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 8,79</t>
+          <t>-5,52; 8,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 5,61</t>
+          <t>-9,54; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 19,18</t>
+          <t>6,86; 19,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,94</t>
+          <t>-4,8; 9,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 3,45</t>
+          <t>-6,92; 2,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 17,37</t>
+          <t>7,95; 17,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 6,93</t>
+          <t>-2,62; 7,27</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-2,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-3,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 7,51</t>
+          <t>-11,6; 8,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 27,6</t>
+          <t>8,91; 27,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 12,66</t>
+          <t>-7,33; 12,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 8,09</t>
+          <t>-12,45; 6,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 28,05</t>
+          <t>9,02; 28,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 14,45</t>
+          <t>-6,41; 13,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 4,97</t>
+          <t>-9,19; 4,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 24,73</t>
+          <t>10,63; 24,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 9,92</t>
+          <t>-3,53; 10,3</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,32</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,08</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,54</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-1,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 4,39</t>
+          <t>-10,59; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 15,19</t>
+          <t>-5,1; 7,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 12,44</t>
+          <t>-11,17; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 3,86</t>
+          <t>-10,32; 5,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 8,3</t>
+          <t>2,1; 15,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 3,26</t>
+          <t>-7,66; 7,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,68</t>
+          <t>-8,28; 1,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 9,33</t>
+          <t>0,24; 9,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 5,34</t>
+          <t>-7,14; 3,48</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,47%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-4,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-3,27%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>10,11%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,47%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,47%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-0,85%</t>
+          <t>-2,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 5,7</t>
+          <t>-12,42; 4,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 19,87</t>
+          <t>-5,83; 9,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 16,52</t>
+          <t>-13,05; 4,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 4,95</t>
+          <t>-12,31; 7,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 10,43</t>
+          <t>2,48; 19,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 3,89</t>
+          <t>-9,11; 9,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 2,15</t>
+          <t>-10,01; 2,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 11,87</t>
+          <t>0,43; 11,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 6,71</t>
+          <t>-8,46; 4,44</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-7,77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-8,11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,39</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,23</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-7,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>-9,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-4,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -1,5</t>
+          <t>-15,45; -1,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 9,13</t>
+          <t>3,4; 14,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,76; -2,71</t>
+          <t>-5,75; 8,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -0,78</t>
+          <t>-14,47; -1,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 15,47</t>
+          <t>-2,34; 9,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 7,51</t>
+          <t>-16,84; -2,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -2,97</t>
+          <t>-12,75; -3,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,16</t>
+          <t>2,52; 10,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 0,81</t>
+          <t>-9,21; 0,33</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,72%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-9,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,02%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,95%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-9,72%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>-11,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,61%</t>
+          <t>-5,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,81; -1,79</t>
+          <t>-18,71; -1,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 11,6</t>
+          <t>4,08; 18,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,15; -3,3</t>
+          <t>-6,75; 10,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,82; -1,24</t>
+          <t>-16,7; -2,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 20,35</t>
+          <t>-2,75; 11,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,76</t>
+          <t>-19,73; -3,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -3,76</t>
+          <t>-15,3; -4,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 12,73</t>
+          <t>3,03; 13,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 1,01</t>
+          <t>-11,06; 0,38</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,22</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,33</t>
+          <t>-5,67; 1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,83</t>
+          <t>5,87; 12,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,8</t>
+          <t>-5,05; 3,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,81</t>
+          <t>-5,88; 1,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,12</t>
+          <t>6,28; 12,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,04</t>
+          <t>-4,84; 2,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,35</t>
+          <t>-4,84; 0,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,58</t>
+          <t>7,12; 11,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,19</t>
+          <t>-4,14; 1,47</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-2,55%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-1,24%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-3,03%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-0,4%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,79%</t>
+          <t>-1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>-1,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,77</t>
+          <t>-7,18; 1,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,88</t>
+          <t>7,43; 16,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,99</t>
+          <t>-6,59; 4,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,38</t>
+          <t>-7,47; 2,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,76; 17,75</t>
+          <t>7,94; 16,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 3,99</t>
+          <t>-6,09; 3,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,47</t>
+          <t>-6,17; 0,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,07; 15,35</t>
+          <t>9,15; 15,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,89</t>
+          <t>-5,37; 1,92</t>
         </is>
       </c>
     </row>
